--- a/2026/BELGRANO 1646/Febrero/Febrero-BLG1646.xlsx
+++ b/2026/BELGRANO 1646/Febrero/Febrero-BLG1646.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\2026\BELGRANO 1646\ENERO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BELGRANO 1646\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F706743-1F45-493E-9E13-70E30369A3A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E980C950-AB51-4F44-B188-43A28AA55016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -1621,6 +1621,9 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1696,6 +1699,9 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1729,6 +1735,9 @@
     <xf numFmtId="0" fontId="24" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="44" fontId="0" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1804,9 +1813,6 @@
     <xf numFmtId="0" fontId="15" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1830,12 +1836,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2203,23 +2203,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N136"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.44140625" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="18.28515625" customWidth="1"/>
+    <col min="13" max="13" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8"/>
       <c r="B1" s="96" t="s">
         <v>118</v>
@@ -2228,7 +2228,7 @@
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="63"/>
       <c r="B2" s="64" t="s">
         <v>0</v>
@@ -2237,7 +2237,7 @@
       <c r="D2" s="64"/>
       <c r="E2" s="65"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="66"/>
       <c r="B3" s="67" t="s">
         <v>88</v>
@@ -2246,7 +2246,7 @@
       <c r="D3" s="67"/>
       <c r="E3" s="68"/>
     </row>
-    <row r="4" spans="1:5" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="66"/>
       <c r="B4" s="67" t="s">
         <v>89</v>
@@ -2255,7 +2255,7 @@
       <c r="D4" s="67"/>
       <c r="E4" s="68"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="69" t="s">
         <v>1</v>
       </c>
@@ -2268,7 +2268,7 @@
       <c r="D5" s="70"/>
       <c r="E5" s="71"/>
     </row>
-    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="66" t="s">
         <v>99</v>
       </c>
@@ -2277,7 +2277,7 @@
       <c r="D6" s="67"/>
       <c r="E6" s="68"/>
     </row>
-    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="69" t="s">
         <v>98</v>
       </c>
@@ -2286,37 +2286,37 @@
       <c r="D7" s="70"/>
       <c r="E7" s="71"/>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="204" t="s">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B14" s="205" t="s">
         <v>134</v>
       </c>
-      <c r="C14" s="205"/>
-      <c r="D14" s="206"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="207"/>
-      <c r="C15" s="208"/>
-      <c r="D15" s="209"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B16" s="207"/>
-      <c r="C16" s="208"/>
-      <c r="D16" s="209"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="210"/>
-      <c r="C17" s="211"/>
-      <c r="D17" s="212"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C14" s="206"/>
+      <c r="D14" s="207"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B15" s="208"/>
+      <c r="C15" s="209"/>
+      <c r="D15" s="210"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B16" s="208"/>
+      <c r="C16" s="209"/>
+      <c r="D16" s="210"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B17" s="211"/>
+      <c r="C17" s="212"/>
+      <c r="D17" s="213"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
     </row>
-    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="60" t="s">
         <v>86</v>
       </c>
@@ -2330,7 +2330,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="119" t="s">
         <v>140</v>
       </c>
@@ -2342,7 +2342,7 @@
       <c r="E22" s="170"/>
       <c r="F22" s="170"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="119" t="s">
         <v>126</v>
       </c>
@@ -2360,7 +2360,7 @@
         <v>116076.08855</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="119" t="s">
         <v>2</v>
       </c>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="G24" s="107"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="119" t="s">
         <v>112</v>
       </c>
@@ -2397,7 +2397,7 @@
         <v>4.6112999999999994E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="119"/>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -2411,7 +2411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="94" t="s">
         <v>3</v>
       </c>
@@ -2438,7 +2438,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="93" t="s">
         <v>109</v>
       </c>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="H28" s="142"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="93"/>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="H29" s="142"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="93"/>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -2483,7 +2483,7 @@
       <c r="F30" s="7"/>
       <c r="H30" s="142"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="93"/>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -2492,7 +2492,7 @@
       <c r="F31" s="7"/>
       <c r="H31" s="142"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="94" t="s">
         <v>117</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="93" t="s">
         <v>109</v>
       </c>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="H33" s="142"/>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>130</v>
       </c>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="H34" s="142"/>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="93" t="s">
         <v>2</v>
       </c>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="H35" s="142"/>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="94" t="s">
         <v>110</v>
       </c>
@@ -2590,7 +2590,7 @@
       </c>
       <c r="H36" s="142"/>
     </row>
-    <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="124"/>
       <c r="B37" s="97"/>
       <c r="C37" s="97"/>
@@ -2599,7 +2599,7 @@
       <c r="F37" s="118"/>
       <c r="H37" s="142"/>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="124"/>
       <c r="B38" s="97"/>
       <c r="C38" s="97"/>
@@ -2608,7 +2608,7 @@
       <c r="F38" s="118"/>
       <c r="H38" s="142"/>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="97"/>
       <c r="B39" s="97"/>
       <c r="C39" s="109"/>
@@ -2617,7 +2617,7 @@
       <c r="F39" s="118"/>
       <c r="H39" s="142"/>
     </row>
-    <row r="40" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="94" t="s">
         <v>117</v>
       </c>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="H40" s="142"/>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="93"/>
       <c r="B41" s="7"/>
       <c r="C41" s="7"/>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="H41" s="142"/>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="93"/>
       <c r="B42" s="7"/>
       <c r="C42" s="97"/>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="H42" s="142"/>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="93"/>
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="H43" s="142"/>
     </row>
-    <row r="44" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="94" t="s">
         <v>127</v>
       </c>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="H44" s="142"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="93" t="s">
         <v>4</v>
       </c>
@@ -2714,7 +2714,7 @@
       <c r="F45" s="99"/>
       <c r="H45" s="142"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="93" t="s">
         <v>154</v>
       </c>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="H46" s="142"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="93" t="s">
         <v>5</v>
       </c>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="H47" s="142"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="93" t="s">
         <v>135</v>
       </c>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="H48" s="142"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="94" t="s">
         <v>6</v>
       </c>
@@ -2803,7 +2803,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
         <v>7</v>
       </c>
@@ -2814,7 +2814,7 @@
       <c r="F50" s="7"/>
       <c r="H50" s="142"/>
     </row>
-    <row r="51" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="166" t="s">
         <v>137</v>
       </c>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="J51" s="160"/>
     </row>
-    <row r="52" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="166" t="s">
         <v>169</v>
       </c>
@@ -2867,7 +2867,7 @@
       <c r="I52" s="160"/>
       <c r="J52" s="160"/>
     </row>
-    <row r="53" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="166" t="s">
         <v>161</v>
       </c>
@@ -2892,7 +2892,7 @@
       <c r="I53" s="160"/>
       <c r="J53" s="160"/>
     </row>
-    <row r="54" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="119" t="s">
         <v>8</v>
       </c>
@@ -2920,7 +2920,7 @@
       <c r="I54" s="160"/>
       <c r="J54" s="160"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="93" t="s">
         <v>151</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="93" t="s">
         <v>151</v>
       </c>
@@ -2982,7 +2982,7 @@
       <c r="I56" s="160"/>
       <c r="J56" s="160"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="93" t="s">
         <v>9</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="93" t="s">
         <v>11</v>
       </c>
@@ -3050,7 +3050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="124" t="s">
         <v>10</v>
       </c>
@@ -3086,12 +3086,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="221" t="s">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" s="222" t="s">
         <v>163</v>
       </c>
-      <c r="B60" s="222"/>
-      <c r="C60" s="223"/>
+      <c r="B60" s="223"/>
+      <c r="C60" s="224"/>
       <c r="D60" s="111">
         <v>55000</v>
       </c>
@@ -3117,7 +3117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="201" t="s">
         <v>173</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="189" t="s">
         <v>165</v>
       </c>
@@ -3176,7 +3176,7 @@
       <c r="I62" s="160"/>
       <c r="J62" s="160"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="189" t="s">
         <v>164</v>
       </c>
@@ -3201,12 +3201,12 @@
       <c r="I63" s="160"/>
       <c r="J63" s="160"/>
     </row>
-    <row r="64" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="229" t="s">
+    <row r="64" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="231" t="s">
         <v>167</v>
       </c>
-      <c r="B64" s="230"/>
-      <c r="C64" s="231"/>
+      <c r="B64" s="232"/>
+      <c r="C64" s="233"/>
       <c r="D64" s="111">
         <v>450000</v>
       </c>
@@ -3226,12 +3226,12 @@
       <c r="I64" s="160"/>
       <c r="J64" s="160"/>
     </row>
-    <row r="65" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="235" t="s">
+    <row r="65" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="237" t="s">
         <v>172</v>
       </c>
-      <c r="B65" s="236"/>
-      <c r="C65" s="237"/>
+      <c r="B65" s="238"/>
+      <c r="C65" s="239"/>
       <c r="D65" s="111">
         <v>120000</v>
       </c>
@@ -3254,8 +3254,8 @@
       <c r="I65" s="160"/>
       <c r="J65" s="160"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="273" t="s">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A66" s="202" t="s">
         <v>174</v>
       </c>
       <c r="B66" s="199"/>
@@ -3282,8 +3282,8 @@
       <c r="I66" s="160"/>
       <c r="J66" s="160"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" s="273" t="s">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A67" s="202" t="s">
         <v>175</v>
       </c>
       <c r="B67" s="199"/>
@@ -3310,8 +3310,8 @@
       <c r="I67" s="160"/>
       <c r="J67" s="160"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="273" t="s">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68" s="202" t="s">
         <v>175</v>
       </c>
       <c r="B68" s="199"/>
@@ -3338,8 +3338,8 @@
       <c r="I68" s="160"/>
       <c r="J68" s="160"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="273" t="s">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A69" s="202" t="s">
         <v>176</v>
       </c>
       <c r="B69" s="199"/>
@@ -3366,7 +3366,7 @@
       <c r="I69" s="160"/>
       <c r="J69" s="160"/>
     </row>
-    <row r="70" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="7" t="s">
         <v>119</v>
       </c>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="272"/>
-      <c r="B71" s="227"/>
-      <c r="C71" s="228"/>
+    <row r="71" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="228"/>
+      <c r="B71" s="229"/>
+      <c r="C71" s="230"/>
       <c r="D71" s="111"/>
       <c r="E71" s="141"/>
       <c r="F71" s="129"/>
@@ -3415,7 +3415,7 @@
       <c r="I71" s="160"/>
       <c r="J71" s="160"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="94" t="s">
         <v>12</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="7"/>
       <c r="B73" s="7"/>
       <c r="C73" s="7"/>
@@ -3455,7 +3455,7 @@
       <c r="F73" s="7"/>
       <c r="H73" s="142"/>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="7"/>
       <c r="B74" s="7"/>
       <c r="C74" s="7"/>
@@ -3464,7 +3464,7 @@
       <c r="F74" s="7"/>
       <c r="H74" s="142"/>
     </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="7"/>
       <c r="B75" s="7"/>
       <c r="C75" s="7"/>
@@ -3473,7 +3473,7 @@
       <c r="F75" s="7"/>
       <c r="H75" s="142"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="124" t="s">
         <v>139</v>
       </c>
@@ -3493,12 +3493,12 @@
       <c r="G76" s="147"/>
       <c r="H76" s="142"/>
     </row>
-    <row r="77" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="232" t="s">
+    <row r="77" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="234" t="s">
         <v>170</v>
       </c>
-      <c r="B77" s="233"/>
-      <c r="C77" s="234"/>
+      <c r="B77" s="235"/>
+      <c r="C77" s="236"/>
       <c r="D77" s="111">
         <v>227600</v>
       </c>
@@ -3510,7 +3510,7 @@
       <c r="H77" s="142"/>
       <c r="I77" s="107"/>
     </row>
-    <row r="78" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="94" t="s">
         <v>16</v>
       </c>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="J78" s="107"/>
     </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="7"/>
       <c r="B79" s="7"/>
       <c r="C79" s="7"/>
@@ -3547,7 +3547,7 @@
       <c r="F79" s="7"/>
       <c r="H79" s="142"/>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="7"/>
       <c r="B80" s="7"/>
       <c r="C80" s="7"/>
@@ -3556,7 +3556,7 @@
       <c r="F80" s="7"/>
       <c r="H80" s="142"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="93" t="s">
         <v>13</v>
       </c>
@@ -3567,7 +3567,7 @@
       <c r="F81" s="7"/>
       <c r="H81" s="142"/>
     </row>
-    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="93" t="s">
         <v>14</v>
       </c>
@@ -3591,7 +3591,7 @@
       </c>
       <c r="H82" s="142"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="93" t="s">
         <v>107</v>
       </c>
@@ -3611,7 +3611,7 @@
       <c r="H83" s="142"/>
       <c r="J83" s="111"/>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="7"/>
       <c r="B84" s="7"/>
       <c r="C84" s="7"/>
@@ -3621,7 +3621,7 @@
       <c r="H84" s="142"/>
       <c r="J84" s="107"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="94" t="s">
         <v>100</v>
       </c>
@@ -3649,7 +3649,7 @@
       </c>
       <c r="J85" s="107"/>
     </row>
-    <row r="86" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="93" t="s">
         <v>100</v>
       </c>
@@ -3660,7 +3660,7 @@
       <c r="F86" s="7"/>
       <c r="H86" s="142"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="93" t="s">
         <v>101</v>
       </c>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="H87" s="142"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="93" t="s">
         <v>102</v>
       </c>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="H88" s="142"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="94" t="s">
         <v>15</v>
       </c>
@@ -3725,7 +3725,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
@@ -3734,7 +3734,7 @@
       <c r="F90" s="7"/>
       <c r="H90" s="142"/>
     </row>
-    <row r="91" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="98" t="s">
         <v>133</v>
       </c>
@@ -3761,7 +3761,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="1"/>
       <c r="D92" s="162"/>
       <c r="E92" s="2"/>
@@ -3769,7 +3769,7 @@
       <c r="G92" s="144"/>
       <c r="H92" s="142"/>
     </row>
-    <row r="93" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
         <v>103</v>
       </c>
@@ -3800,11 +3800,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D94" s="162"/>
       <c r="E94" s="107"/>
     </row>
-    <row r="95" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="169" t="s">
         <v>150</v>
       </c>
@@ -3812,17 +3812,17 @@
       <c r="C95" s="136"/>
       <c r="E95" s="107"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="C96" s="134"/>
       <c r="E96" s="107"/>
     </row>
-    <row r="97" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="1"/>
       <c r="C97" s="134"/>
       <c r="E97" s="107"/>
     </row>
-    <row r="98" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="137" t="s">
         <v>29</v>
       </c>
@@ -3833,19 +3833,19 @@
       </c>
       <c r="E98" s="107"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E99" s="107"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E100" s="132"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" s="219" t="s">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A101" s="220" t="s">
         <v>113</v>
       </c>
-      <c r="B101" s="220"/>
-      <c r="C101" s="220"/>
-      <c r="D101" s="220"/>
+      <c r="B101" s="221"/>
+      <c r="C101" s="221"/>
+      <c r="D101" s="221"/>
       <c r="E101" s="155" t="s">
         <v>21</v>
       </c>
@@ -3853,10 +3853,10 @@
         <v>122</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="216"/>
-      <c r="B102" s="217"/>
-      <c r="C102" s="218"/>
+    <row r="102" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="217"/>
+      <c r="B102" s="218"/>
+      <c r="C102" s="219"/>
       <c r="D102" s="111"/>
       <c r="E102" s="141">
         <f t="shared" ref="E102:E103" si="32">D102*91.91%</f>
@@ -3867,10 +3867,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="224"/>
-      <c r="B103" s="225"/>
-      <c r="C103" s="226"/>
+    <row r="103" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="225"/>
+      <c r="B103" s="226"/>
+      <c r="C103" s="227"/>
       <c r="D103" s="111"/>
       <c r="E103" s="141">
         <f t="shared" si="32"/>
@@ -3881,12 +3881,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="213" t="s">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A104" s="214" t="s">
         <v>29</v>
       </c>
-      <c r="B104" s="214"/>
-      <c r="C104" s="215"/>
+      <c r="B104" s="215"/>
+      <c r="C104" s="216"/>
       <c r="D104" s="154">
         <f>SUM(D102:D103)</f>
         <v>0</v>
@@ -3908,10 +3908,10 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E106" s="107"/>
     </row>
-    <row r="107" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="101" t="s">
         <v>104</v>
       </c>
@@ -3920,7 +3920,7 @@
         <v>8500000</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="103" t="s">
         <v>106</v>
       </c>
@@ -3929,20 +3929,20 @@
         <v>7864396.8099999996</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D109" s="203"/>
-      <c r="E109" s="203"/>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D109" s="204"/>
+      <c r="E109" s="204"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="73" t="s">
         <v>90</v>
       </c>
       <c r="B110" s="74"/>
       <c r="C110" s="75"/>
-      <c r="D110" s="203"/>
-      <c r="E110" s="203"/>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D110" s="204"/>
+      <c r="E110" s="204"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="76" t="s">
         <v>91</v>
       </c>
@@ -3950,10 +3950,10 @@
         <v>2579766.3959282823</v>
       </c>
       <c r="C111" s="77"/>
-      <c r="D111" s="203"/>
-      <c r="E111" s="203"/>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D111" s="204"/>
+      <c r="E111" s="204"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="78" t="s">
         <v>92</v>
       </c>
@@ -3964,10 +3964,10 @@
       <c r="C112" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="D112" s="203"/>
-      <c r="E112" s="203"/>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D112" s="204"/>
+      <c r="E112" s="204"/>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="78" t="s">
         <v>115</v>
       </c>
@@ -3976,11 +3976,11 @@
         <v>-7864396.8099999996</v>
       </c>
       <c r="C113" s="75"/>
-      <c r="D113" s="203"/>
-      <c r="E113" s="203"/>
+      <c r="D113" s="204"/>
+      <c r="E113" s="204"/>
       <c r="G113" s="111"/>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="78" t="s">
         <v>114</v>
       </c>
@@ -3989,11 +3989,11 @@
         <v>0</v>
       </c>
       <c r="C114" s="75"/>
-      <c r="D114" s="203"/>
-      <c r="E114" s="203"/>
+      <c r="D114" s="204"/>
+      <c r="E114" s="204"/>
       <c r="G114" s="121"/>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="78" t="s">
         <v>105</v>
       </c>
@@ -4003,7 +4003,7 @@
       </c>
       <c r="C115" s="79"/>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="78" t="s">
         <v>120</v>
       </c>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C116" s="79"/>
     </row>
-    <row r="117" spans="1:7" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="198" t="s">
         <v>166</v>
       </c>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C117" s="143"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="76" t="s">
         <v>94</v>
       </c>
@@ -4032,17 +4032,17 @@
       </c>
       <c r="C118" s="143"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="79"/>
       <c r="C119" s="75"/>
       <c r="D119" s="82"/>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C120" s="75"/>
       <c r="D120" s="107"/>
       <c r="E120" s="160"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="73" t="s">
         <v>95</v>
       </c>
@@ -4054,7 +4054,7 @@
       <c r="E121" s="160"/>
       <c r="F121" s="160"/>
     </row>
-    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="76" t="s">
         <v>159</v>
       </c>
@@ -4065,19 +4065,19 @@
       <c r="D122" s="160"/>
       <c r="E122" s="167"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="76"/>
       <c r="B123" s="157"/>
       <c r="C123" s="81"/>
       <c r="E123" s="107"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="76"/>
       <c r="B124" s="157"/>
       <c r="C124" s="81"/>
       <c r="E124" s="107"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="99" t="s">
         <v>29</v>
       </c>
@@ -4087,46 +4087,46 @@
       </c>
       <c r="C125" s="81"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C126" s="82"/>
       <c r="D126" s="160"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B127" s="79"/>
       <c r="C127" s="75"/>
     </row>
-    <row r="129" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:14" x14ac:dyDescent="0.3">
       <c r="N129" s="11"/>
     </row>
-    <row r="132" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B132" s="202"/>
-      <c r="C132" s="202"/>
-      <c r="D132" s="202"/>
-      <c r="E132" s="202"/>
-    </row>
-    <row r="133" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B133" s="202"/>
-      <c r="C133" s="202"/>
-      <c r="D133" s="202"/>
-      <c r="E133" s="202"/>
-    </row>
-    <row r="134" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B134" s="202"/>
-      <c r="C134" s="202"/>
-      <c r="D134" s="202"/>
-      <c r="E134" s="202"/>
-    </row>
-    <row r="135" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B135" s="202"/>
-      <c r="C135" s="202"/>
-      <c r="D135" s="202"/>
-      <c r="E135" s="202"/>
-    </row>
-    <row r="136" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B136" s="202"/>
-      <c r="C136" s="202"/>
-      <c r="D136" s="202"/>
-      <c r="E136" s="202"/>
+    <row r="132" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B132" s="203"/>
+      <c r="C132" s="203"/>
+      <c r="D132" s="203"/>
+      <c r="E132" s="203"/>
+    </row>
+    <row r="133" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B133" s="203"/>
+      <c r="C133" s="203"/>
+      <c r="D133" s="203"/>
+      <c r="E133" s="203"/>
+    </row>
+    <row r="134" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B134" s="203"/>
+      <c r="C134" s="203"/>
+      <c r="D134" s="203"/>
+      <c r="E134" s="203"/>
+    </row>
+    <row r="135" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B135" s="203"/>
+      <c r="C135" s="203"/>
+      <c r="D135" s="203"/>
+      <c r="E135" s="203"/>
+    </row>
+    <row r="136" spans="2:14" x14ac:dyDescent="0.3">
+      <c r="B136" s="203"/>
+      <c r="C136" s="203"/>
+      <c r="D136" s="203"/>
+      <c r="E136" s="203"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -4152,62 +4152,62 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R63"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="6.140625" customWidth="1"/>
-    <col min="6" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="6.109375" customWidth="1"/>
+    <col min="6" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.109375" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" customWidth="1"/>
-    <col min="14" max="14" width="13.7109375" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" customWidth="1"/>
+    <col min="14" max="14" width="13.6640625" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" customWidth="1"/>
+    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="251"/>
-      <c r="B1" s="252"/>
-      <c r="C1" s="252"/>
-      <c r="D1" s="252"/>
-      <c r="E1" s="252"/>
-      <c r="F1" s="252"/>
-      <c r="G1" s="252"/>
-      <c r="H1" s="252"/>
-      <c r="I1" s="252"/>
-      <c r="J1" s="253"/>
+    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="254"/>
+      <c r="B1" s="255"/>
+      <c r="C1" s="255"/>
+      <c r="D1" s="255"/>
+      <c r="E1" s="255"/>
+      <c r="F1" s="255"/>
+      <c r="G1" s="255"/>
+      <c r="H1" s="255"/>
+      <c r="I1" s="255"/>
+      <c r="J1" s="256"/>
       <c r="K1" s="178" t="s">
         <v>124</v>
       </c>
-      <c r="L1" s="238">
+      <c r="L1" s="241">
         <f>RESUMEN!D93</f>
         <v>8500000</v>
       </c>
-      <c r="M1" s="239"/>
+      <c r="M1" s="242"/>
       <c r="N1" s="179"/>
       <c r="O1" s="130">
         <f>L1*8.09%</f>
         <v>687650</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="254"/>
-      <c r="B2" s="255"/>
-      <c r="C2" s="255"/>
-      <c r="D2" s="255"/>
-      <c r="E2" s="255"/>
-      <c r="F2" s="255"/>
-      <c r="G2" s="255"/>
-      <c r="H2" s="255"/>
-      <c r="I2" s="255"/>
-      <c r="J2" s="256"/>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" s="257"/>
+      <c r="B2" s="258"/>
+      <c r="C2" s="258"/>
+      <c r="D2" s="258"/>
+      <c r="E2" s="258"/>
+      <c r="F2" s="258"/>
+      <c r="G2" s="258"/>
+      <c r="H2" s="258"/>
+      <c r="I2" s="258"/>
+      <c r="J2" s="259"/>
       <c r="K2" s="180" t="s">
         <v>125</v>
       </c>
@@ -4221,17 +4221,17 @@
         <v>63720.213143000146</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="254"/>
-      <c r="B3" s="255"/>
-      <c r="C3" s="255"/>
-      <c r="D3" s="255"/>
-      <c r="E3" s="255"/>
-      <c r="F3" s="255"/>
-      <c r="G3" s="255"/>
-      <c r="H3" s="255"/>
-      <c r="I3" s="255"/>
-      <c r="J3" s="256"/>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" s="257"/>
+      <c r="B3" s="258"/>
+      <c r="C3" s="258"/>
+      <c r="D3" s="258"/>
+      <c r="E3" s="258"/>
+      <c r="F3" s="258"/>
+      <c r="G3" s="258"/>
+      <c r="H3" s="258"/>
+      <c r="I3" s="258"/>
+      <c r="J3" s="259"/>
       <c r="K3" s="180" t="s">
         <v>131</v>
       </c>
@@ -4243,17 +4243,17 @@
       <c r="N3" s="184"/>
       <c r="O3" s="72"/>
     </row>
-    <row r="4" spans="1:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="257"/>
-      <c r="B4" s="258"/>
-      <c r="C4" s="258"/>
-      <c r="D4" s="258"/>
-      <c r="E4" s="258"/>
-      <c r="F4" s="258"/>
-      <c r="G4" s="258"/>
-      <c r="H4" s="258"/>
-      <c r="I4" s="258"/>
-      <c r="J4" s="259"/>
+    <row r="4" spans="1:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="260"/>
+      <c r="B4" s="261"/>
+      <c r="C4" s="261"/>
+      <c r="D4" s="261"/>
+      <c r="E4" s="261"/>
+      <c r="F4" s="261"/>
+      <c r="G4" s="261"/>
+      <c r="H4" s="261"/>
+      <c r="I4" s="261"/>
+      <c r="J4" s="262"/>
       <c r="K4" s="185" t="s">
         <v>125</v>
       </c>
@@ -4267,67 +4267,67 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="242" t="s">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" s="245" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="260" t="s">
+      <c r="B5" s="263" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="242" t="s">
+      <c r="C5" s="245" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="249" t="s">
+      <c r="D5" s="252" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="242" t="s">
+      <c r="E5" s="245" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="242" t="s">
+      <c r="F5" s="245" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="242" t="s">
+      <c r="G5" s="245" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="244" t="s">
+      <c r="H5" s="247" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="249" t="s">
+      <c r="I5" s="252" t="s">
         <v>108</v>
       </c>
-      <c r="J5" s="240" t="s">
+      <c r="J5" s="243" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="240" t="s">
+      <c r="K5" s="243" t="s">
         <v>69</v>
       </c>
-      <c r="L5" s="247" t="s">
+      <c r="L5" s="250" t="s">
         <v>123</v>
       </c>
-      <c r="M5" s="240" t="s">
+      <c r="M5" s="243" t="s">
         <v>67</v>
       </c>
-      <c r="N5" s="240" t="s">
+      <c r="N5" s="243" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="243"/>
-      <c r="B6" s="261"/>
-      <c r="C6" s="243"/>
-      <c r="D6" s="262"/>
-      <c r="E6" s="243"/>
-      <c r="F6" s="243"/>
-      <c r="G6" s="243"/>
-      <c r="H6" s="245"/>
-      <c r="I6" s="250"/>
-      <c r="J6" s="241"/>
-      <c r="K6" s="246"/>
-      <c r="L6" s="248"/>
-      <c r="M6" s="246"/>
-      <c r="N6" s="241"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" s="246"/>
+      <c r="B6" s="264"/>
+      <c r="C6" s="246"/>
+      <c r="D6" s="265"/>
+      <c r="E6" s="246"/>
+      <c r="F6" s="246"/>
+      <c r="G6" s="246"/>
+      <c r="H6" s="248"/>
+      <c r="I6" s="253"/>
+      <c r="J6" s="244"/>
+      <c r="K6" s="249"/>
+      <c r="L6" s="251"/>
+      <c r="M6" s="249"/>
+      <c r="N6" s="244"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>33</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>660626.7540684198</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>35</v>
       </c>
@@ -4416,7 +4416,7 @@
         <v>221285.17970772015</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>35</v>
       </c>
@@ -4462,7 +4462,7 @@
         <v>422459.75237298582</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>38</v>
       </c>
@@ -4508,7 +4508,7 @@
         <v>284984.53333333333</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>38</v>
       </c>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="P11" s="107"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>41</v>
       </c>
@@ -4601,7 +4601,7 @@
         <v>284984.53333333333</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>41</v>
       </c>
@@ -4647,7 +4647,7 @@
         <v>344189.93313106295</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>43</v>
       </c>
@@ -4693,7 +4693,7 @@
         <v>284984.53333333333</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>43</v>
       </c>
@@ -4734,7 +4734,7 @@
         <v>688377.99658965948</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>46</v>
       </c>
@@ -4780,7 +4780,7 @@
         <v>305033.45794995333</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>46</v>
       </c>
@@ -4828,7 +4828,7 @@
         <v>365389.03911844839</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>48</v>
       </c>
@@ -4877,7 +4877,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>48</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>344189.58216074487</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>51</v>
       </c>
@@ -4969,7 +4969,7 @@
         <v>284984.16854183254</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>51</v>
       </c>
@@ -5015,7 +5015,7 @@
         <v>344188.94862697041</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>54</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>284984.53333333333</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>54</v>
       </c>
@@ -5107,7 +5107,7 @@
         <v>665935.33457008889</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>56</v>
       </c>
@@ -5153,7 +5153,7 @@
         <v>284354.22915967251</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>56</v>
       </c>
@@ -5204,7 +5204,7 @@
       <c r="Q25" s="133"/>
       <c r="R25" s="133"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>59</v>
       </c>
@@ -5250,7 +5250,7 @@
         <v>-1081749.0877740008</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>61</v>
       </c>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="R27" s="133"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>63</v>
       </c>
@@ -5343,7 +5343,7 @@
         <v>590060.84496279992</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>65</v>
       </c>
@@ -5384,7 +5384,7 @@
         <v>1182084.4795274353</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="122" t="s">
         <v>96</v>
       </c>
@@ -5428,7 +5428,7 @@
         <v>54187.199999999997</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="122" t="s">
         <v>96</v>
       </c>
@@ -5472,7 +5472,7 @@
         <v>55190.666666666664</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="122" t="s">
         <v>96</v>
       </c>
@@ -5516,7 +5516,7 @@
         <v>45156</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="122" t="s">
         <v>96</v>
       </c>
@@ -5560,7 +5560,7 @@
         <v>61211.466666666667</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="122" t="s">
         <v>96</v>
       </c>
@@ -5604,7 +5604,7 @@
         <v>54187.199999999997</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="122" t="s">
         <v>96</v>
       </c>
@@ -5645,7 +5645,7 @@
         <v>100346.66666666667</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="122" t="s">
         <v>96</v>
       </c>
@@ -5689,7 +5689,7 @@
         <v>50173.333333333336</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="122" t="s">
         <v>96</v>
       </c>
@@ -5733,7 +5733,7 @@
         <v>49169.866666666661</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="122" t="s">
         <v>96</v>
       </c>
@@ -5777,7 +5777,7 @@
         <v>49169.866666666661</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="122" t="s">
         <v>96</v>
       </c>
@@ -5821,7 +5821,7 @@
         <v>59204.533333333333</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="122" t="s">
         <v>96</v>
       </c>
@@ -5865,7 +5865,7 @@
         <v>57197.599999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="122" t="s">
         <v>96</v>
       </c>
@@ -5909,7 +5909,7 @@
         <v>54187.199999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="122" t="s">
         <v>96</v>
       </c>
@@ -5950,7 +5950,7 @@
         <v>110381.33333333333</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="122" t="s">
         <v>96</v>
       </c>
@@ -5995,7 +5995,7 @@
         <v>64417.213143000379</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="122" t="s">
         <v>96</v>
       </c>
@@ -6036,7 +6036,7 @@
         <v>122422.93333333333</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="122" t="s">
         <v>96</v>
       </c>
@@ -6080,7 +6080,7 @@
         <v>54187.199999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="122" t="s">
         <v>96</v>
       </c>
@@ -6127,7 +6127,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="122" t="s">
         <v>96</v>
       </c>
@@ -6176,7 +6176,7 @@
         <v>-888463.33333333314</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="122" t="s">
         <v>96</v>
       </c>
@@ -6220,7 +6220,7 @@
         <v>49169.866666666661</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="122" t="s">
         <v>96</v>
       </c>
@@ -6265,7 +6265,7 @@
         <v>49169.866666666661</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" s="122" t="s">
         <v>96</v>
       </c>
@@ -6309,7 +6309,7 @@
         <v>59204.533333333333</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" s="122" t="s">
         <v>96</v>
       </c>
@@ -6353,7 +6353,7 @@
         <v>57197.599999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="88"/>
       <c r="B52" s="88"/>
       <c r="C52" s="88"/>
@@ -6394,41 +6394,41 @@
       </c>
       <c r="P52" s="130"/>
     </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="K53" s="133">
         <f>K52-L1</f>
         <v>-64417.213143000379</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="263"/>
-      <c r="D54" s="263"/>
-      <c r="E54" s="263"/>
-      <c r="F54" s="263"/>
-      <c r="G54" s="263"/>
-      <c r="H54" s="263"/>
-      <c r="I54" s="263"/>
-      <c r="J54" s="263"/>
-      <c r="K54" s="263"/>
-      <c r="L54" s="263"/>
-      <c r="M54" s="263"/>
-      <c r="N54" s="263"/>
-    </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="263"/>
-      <c r="D55" s="263"/>
-      <c r="E55" s="263"/>
-      <c r="F55" s="263"/>
-      <c r="G55" s="263"/>
-      <c r="H55" s="263"/>
-      <c r="I55" s="263"/>
-      <c r="J55" s="263"/>
-      <c r="K55" s="263"/>
-      <c r="L55" s="263"/>
-      <c r="M55" s="263"/>
-      <c r="N55" s="263"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C54" s="240"/>
+      <c r="D54" s="240"/>
+      <c r="E54" s="240"/>
+      <c r="F54" s="240"/>
+      <c r="G54" s="240"/>
+      <c r="H54" s="240"/>
+      <c r="I54" s="240"/>
+      <c r="J54" s="240"/>
+      <c r="K54" s="240"/>
+      <c r="L54" s="240"/>
+      <c r="M54" s="240"/>
+      <c r="N54" s="240"/>
+    </row>
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C55" s="240"/>
+      <c r="D55" s="240"/>
+      <c r="E55" s="240"/>
+      <c r="F55" s="240"/>
+      <c r="G55" s="240"/>
+      <c r="H55" s="240"/>
+      <c r="I55" s="240"/>
+      <c r="J55" s="240"/>
+      <c r="K55" s="240"/>
+      <c r="L55" s="240"/>
+      <c r="M55" s="240"/>
+      <c r="N55" s="240"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C56" s="152"/>
       <c r="D56" s="152"/>
       <c r="E56" s="152"/>
@@ -6442,108 +6442,110 @@
       <c r="M56" s="152"/>
       <c r="N56" s="152"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C57" s="263" t="s">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C57" s="240" t="s">
         <v>129</v>
       </c>
-      <c r="D57" s="263"/>
-      <c r="E57" s="263"/>
-      <c r="F57" s="263"/>
-      <c r="G57" s="263"/>
-      <c r="H57" s="263"/>
-      <c r="I57" s="263"/>
-      <c r="J57" s="263"/>
-      <c r="K57" s="263"/>
-      <c r="L57" s="263"/>
-      <c r="M57" s="263"/>
-      <c r="N57" s="263"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C58" s="263"/>
-      <c r="D58" s="263"/>
-      <c r="E58" s="263"/>
-      <c r="F58" s="263"/>
-      <c r="G58" s="263"/>
-      <c r="H58" s="263"/>
-      <c r="I58" s="263"/>
-      <c r="J58" s="263"/>
-      <c r="K58" s="263"/>
-      <c r="L58" s="263"/>
-      <c r="M58" s="263"/>
-      <c r="N58" s="263"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C59" s="263"/>
-      <c r="D59" s="263"/>
-      <c r="E59" s="263"/>
-      <c r="F59" s="263"/>
-      <c r="G59" s="263"/>
-      <c r="H59" s="263"/>
-      <c r="I59" s="263"/>
-      <c r="J59" s="263"/>
-      <c r="K59" s="263"/>
-      <c r="L59" s="263"/>
-      <c r="M59" s="263"/>
-      <c r="N59" s="263"/>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C60" s="263"/>
-      <c r="D60" s="263"/>
-      <c r="E60" s="263"/>
-      <c r="F60" s="263"/>
-      <c r="G60" s="263"/>
-      <c r="H60" s="263"/>
-      <c r="I60" s="263"/>
-      <c r="J60" s="263"/>
-      <c r="K60" s="263"/>
-      <c r="L60" s="263"/>
-      <c r="M60" s="263"/>
-      <c r="N60" s="263"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C61" s="263"/>
-      <c r="D61" s="263"/>
-      <c r="E61" s="263"/>
-      <c r="F61" s="263"/>
-      <c r="G61" s="263"/>
-      <c r="H61" s="263"/>
-      <c r="I61" s="263"/>
-      <c r="J61" s="263"/>
-      <c r="K61" s="263"/>
-      <c r="L61" s="263"/>
-      <c r="M61" s="263"/>
-      <c r="N61" s="263"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C62" s="263"/>
-      <c r="D62" s="263"/>
-      <c r="E62" s="263"/>
-      <c r="F62" s="263"/>
-      <c r="G62" s="263"/>
-      <c r="H62" s="263"/>
-      <c r="I62" s="263"/>
-      <c r="J62" s="263"/>
-      <c r="K62" s="263"/>
-      <c r="L62" s="263"/>
-      <c r="M62" s="263"/>
-      <c r="N62" s="263"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C63" s="263"/>
-      <c r="D63" s="263"/>
-      <c r="E63" s="263"/>
-      <c r="F63" s="263"/>
-      <c r="G63" s="263"/>
-      <c r="H63" s="263"/>
-      <c r="I63" s="263"/>
-      <c r="J63" s="263"/>
-      <c r="K63" s="263"/>
-      <c r="L63" s="263"/>
-      <c r="M63" s="263"/>
-      <c r="N63" s="263"/>
+      <c r="D57" s="240"/>
+      <c r="E57" s="240"/>
+      <c r="F57" s="240"/>
+      <c r="G57" s="240"/>
+      <c r="H57" s="240"/>
+      <c r="I57" s="240"/>
+      <c r="J57" s="240"/>
+      <c r="K57" s="240"/>
+      <c r="L57" s="240"/>
+      <c r="M57" s="240"/>
+      <c r="N57" s="240"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C58" s="240"/>
+      <c r="D58" s="240"/>
+      <c r="E58" s="240"/>
+      <c r="F58" s="240"/>
+      <c r="G58" s="240"/>
+      <c r="H58" s="240"/>
+      <c r="I58" s="240"/>
+      <c r="J58" s="240"/>
+      <c r="K58" s="240"/>
+      <c r="L58" s="240"/>
+      <c r="M58" s="240"/>
+      <c r="N58" s="240"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C59" s="240"/>
+      <c r="D59" s="240"/>
+      <c r="E59" s="240"/>
+      <c r="F59" s="240"/>
+      <c r="G59" s="240"/>
+      <c r="H59" s="240"/>
+      <c r="I59" s="240"/>
+      <c r="J59" s="240"/>
+      <c r="K59" s="240"/>
+      <c r="L59" s="240"/>
+      <c r="M59" s="240"/>
+      <c r="N59" s="240"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C60" s="240"/>
+      <c r="D60" s="240"/>
+      <c r="E60" s="240"/>
+      <c r="F60" s="240"/>
+      <c r="G60" s="240"/>
+      <c r="H60" s="240"/>
+      <c r="I60" s="240"/>
+      <c r="J60" s="240"/>
+      <c r="K60" s="240"/>
+      <c r="L60" s="240"/>
+      <c r="M60" s="240"/>
+      <c r="N60" s="240"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C61" s="240"/>
+      <c r="D61" s="240"/>
+      <c r="E61" s="240"/>
+      <c r="F61" s="240"/>
+      <c r="G61" s="240"/>
+      <c r="H61" s="240"/>
+      <c r="I61" s="240"/>
+      <c r="J61" s="240"/>
+      <c r="K61" s="240"/>
+      <c r="L61" s="240"/>
+      <c r="M61" s="240"/>
+      <c r="N61" s="240"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C62" s="240"/>
+      <c r="D62" s="240"/>
+      <c r="E62" s="240"/>
+      <c r="F62" s="240"/>
+      <c r="G62" s="240"/>
+      <c r="H62" s="240"/>
+      <c r="I62" s="240"/>
+      <c r="J62" s="240"/>
+      <c r="K62" s="240"/>
+      <c r="L62" s="240"/>
+      <c r="M62" s="240"/>
+      <c r="N62" s="240"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C63" s="240"/>
+      <c r="D63" s="240"/>
+      <c r="E63" s="240"/>
+      <c r="F63" s="240"/>
+      <c r="G63" s="240"/>
+      <c r="H63" s="240"/>
+      <c r="I63" s="240"/>
+      <c r="J63" s="240"/>
+      <c r="K63" s="240"/>
+      <c r="L63" s="240"/>
+      <c r="M63" s="240"/>
+      <c r="N63" s="240"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="C57:N63"/>
     <mergeCell ref="C54:N55"/>
     <mergeCell ref="L1:M1"/>
@@ -6560,8 +6562,6 @@
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -6571,17 +6571,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{596D2FF5-218B-41A1-9BCB-F43114942886}">
   <dimension ref="C4:H25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="14.85546875" customWidth="1"/>
+    <col min="4" max="4" width="14.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>142</v>
       </c>
@@ -6589,7 +6589,7 @@
         <v>-447223.45918396302</v>
       </c>
     </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>143</v>
       </c>
@@ -6597,7 +6597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>144</v>
       </c>
@@ -6605,7 +6605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>145</v>
       </c>
@@ -6613,12 +6613,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C10" s="3" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
         <v>142</v>
       </c>
@@ -6626,7 +6626,7 @@
         <v>451182</v>
       </c>
     </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C12" t="s">
         <v>143</v>
       </c>
@@ -6634,7 +6634,7 @@
         <v>40606.380000000005</v>
       </c>
     </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
         <v>144</v>
       </c>
@@ -6642,7 +6642,7 @@
         <v>41358.350000000006</v>
       </c>
     </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
         <v>145</v>
       </c>
@@ -6650,7 +6650,7 @@
         <v>37598.5</v>
       </c>
     </row>
-    <row r="16" spans="3:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C16" s="3" t="s">
         <v>146</v>
       </c>
@@ -6660,7 +6660,7 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
         <v>142</v>
       </c>
@@ -6669,7 +6669,7 @@
         <v>3958.5408160369843</v>
       </c>
     </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
         <v>143</v>
       </c>
@@ -6677,7 +6677,7 @@
         <v>40606.380000000005</v>
       </c>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
         <v>144</v>
       </c>
@@ -6685,7 +6685,7 @@
         <v>41358.350000000006</v>
       </c>
     </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
         <v>145</v>
       </c>
@@ -6693,7 +6693,7 @@
         <v>37598.5</v>
       </c>
     </row>
-    <row r="21" spans="3:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C21" t="s">
         <v>149</v>
       </c>
@@ -6701,26 +6701,26 @@
         <v>-25000</v>
       </c>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C22" s="264" t="s">
+    <row r="22" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C22" s="266" t="s">
         <v>148</v>
       </c>
-      <c r="D22" s="267">
+      <c r="D22" s="269">
         <f>SUM(D17:D21)</f>
         <v>98521.770816036995</v>
       </c>
     </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C23" s="265"/>
-      <c r="D23" s="268"/>
-    </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C24" s="265"/>
-      <c r="D24" s="268"/>
-    </row>
-    <row r="25" spans="3:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="266"/>
-      <c r="D25" s="269"/>
+    <row r="23" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C23" s="267"/>
+      <c r="D23" s="270"/>
+    </row>
+    <row r="24" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C24" s="267"/>
+      <c r="D24" s="270"/>
+    </row>
+    <row r="25" spans="3:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C25" s="268"/>
+      <c r="D25" s="271"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6735,16 +6735,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.85546875" customWidth="1"/>
-    <col min="12" max="12" width="13.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="8.44140625" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" customWidth="1"/>
+    <col min="12" max="12" width="13.6640625" customWidth="1"/>
+    <col min="13" max="13" width="11.44140625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="47"/>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="O1" s="51"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="48"/>
       <c r="B2" s="50"/>
       <c r="C2" s="50"/>
@@ -6787,7 +6787,7 @@
       <c r="N2" s="48"/>
       <c r="O2" s="48"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="48"/>
       <c r="B3" s="50"/>
       <c r="C3" s="50"/>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="O3" s="53"/>
     </row>
-    <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="48"/>
       <c r="B4" s="50"/>
       <c r="C4" s="50"/>
@@ -6831,11 +6831,11 @@
       <c r="N4" s="48"/>
       <c r="O4" s="48"/>
     </row>
-    <row r="5" spans="1:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="270" t="s">
+    <row r="5" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="272" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="270" t="s">
+      <c r="B5" s="272" t="s">
         <v>22</v>
       </c>
       <c r="C5" s="54" t="s">
@@ -6847,7 +6847,7 @@
       <c r="E5" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="270" t="s">
+      <c r="F5" s="272" t="s">
         <v>75</v>
       </c>
       <c r="G5" s="36" t="s">
@@ -6869,16 +6869,16 @@
         <v>29</v>
       </c>
       <c r="M5" s="40"/>
-      <c r="N5" s="270" t="s">
+      <c r="N5" s="272" t="s">
         <v>78</v>
       </c>
-      <c r="O5" s="270" t="s">
+      <c r="O5" s="272" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="271"/>
-      <c r="B6" s="271"/>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="273"/>
+      <c r="B6" s="273"/>
       <c r="C6" s="55" t="s">
         <v>80</v>
       </c>
@@ -6888,7 +6888,7 @@
       <c r="E6" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="271"/>
+      <c r="F6" s="273"/>
       <c r="G6" s="43" t="s">
         <v>81</v>
       </c>
@@ -6908,10 +6908,10 @@
         <v>84</v>
       </c>
       <c r="M6" s="46"/>
-      <c r="N6" s="271"/>
-      <c r="O6" s="271"/>
-    </row>
-    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N6" s="273"/>
+      <c r="O6" s="273"/>
+    </row>
+    <row r="7" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14">
         <v>1</v>
       </c>
@@ -6957,7 +6957,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14">
         <v>2</v>
       </c>
@@ -7003,7 +7003,7 @@
         <v>12569.682901267399</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14">
         <v>3</v>
       </c>
@@ -7049,7 +7049,7 @@
         <v>9919.7751374005984</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14">
         <v>4</v>
       </c>
@@ -7095,7 +7095,7 @@
         <v>14159.627559587479</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14">
         <v>5</v>
       </c>
@@ -7141,7 +7141,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14">
         <v>6</v>
       </c>
@@ -7187,7 +7187,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14">
         <v>7</v>
       </c>
@@ -7233,7 +7233,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14">
         <v>8</v>
       </c>
@@ -7279,7 +7279,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14">
         <v>9</v>
       </c>
@@ -7325,7 +7325,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14">
         <v>10</v>
       </c>
@@ -7371,7 +7371,7 @@
         <v>13629.64600681412</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14">
         <v>11</v>
       </c>
@@ -7417,7 +7417,7 @@
         <v>13099.66445404076</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14">
         <v>12</v>
       </c>
@@ -7463,7 +7463,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="14">
         <v>13</v>
       </c>
@@ -7509,7 +7509,7 @@
         <v>12569.682901267399</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14">
         <v>14</v>
       </c>
@@ -7555,7 +7555,7 @@
         <v>9919.7751374005984</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="14">
         <v>15</v>
       </c>
@@ -7601,7 +7601,7 @@
         <v>14159.627559587479</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14">
         <v>16</v>
       </c>
@@ -7647,7 +7647,7 @@
         <v>12304.692124880721</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="14">
         <v>17</v>
       </c>
@@ -7693,7 +7693,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="14">
         <v>18</v>
       </c>
@@ -7739,7 +7739,7 @@
         <v>11244.729019334</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="14">
         <v>19</v>
       </c>
@@ -7785,7 +7785,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="14">
         <v>20</v>
       </c>
@@ -7831,7 +7831,7 @@
         <v>10979.738242947318</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="14">
         <v>21</v>
       </c>
@@ -7877,7 +7877,7 @@
         <v>13629.64600681412</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14">
         <v>22</v>
       </c>
@@ -7923,7 +7923,7 @@
         <v>13099.66445404076</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="14"/>
       <c r="B29" s="33"/>
       <c r="C29" s="33"/>
@@ -7940,7 +7940,7 @@
       <c r="N29" s="6"/>
       <c r="O29" s="6"/>
     </row>
-    <row r="30" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="12"/>
       <c r="B30" s="13"/>
       <c r="C30" s="56">
@@ -7981,7 +7981,7 @@
         <v>264873.42966686888</v>
       </c>
     </row>
-    <row r="33" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="5:6" x14ac:dyDescent="0.3">
       <c r="E33" s="32"/>
       <c r="F33" s="32"/>
     </row>

--- a/2026/BELGRANO 1646/Febrero/Febrero-BLG1646.xlsx
+++ b/2026/BELGRANO 1646/Febrero/Febrero-BLG1646.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Escritorio\rc-consorcio2025\2026\BELGRANO 1646\Febrero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BELGRANO 1646\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48CC2B12-3124-4BD0-A972-61678A240989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F5539AC-7531-4524-9655-0FC494829BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -20,20 +20,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$64</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$116</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -500,14 +487,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="168" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
   </numFmts>
   <fonts count="22" x14ac:knownFonts="1">
     <font>
@@ -1048,8 +1035,8 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="201">
@@ -1063,96 +1050,96 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="4" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="2" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="8" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="8" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="8" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="6" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="8" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1162,34 +1149,34 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="9" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="7" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="15" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="6" fontId="4" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="4" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1237,7 +1224,7 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="2" fillId="3" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="43" fontId="2" fillId="3" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1306,7 +1293,7 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1324,10 +1311,13 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1393,13 +1383,10 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="3" builtinId="3"/>
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="Millares" xfId="3" builtinId="3"/>
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Moneda 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -1762,23 +1749,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N126"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.453125" customWidth="1"/>
-    <col min="2" max="2" width="36.90625" customWidth="1"/>
-    <col min="3" max="3" width="17.453125" customWidth="1"/>
-    <col min="4" max="4" width="21.6328125" customWidth="1"/>
-    <col min="5" max="5" width="15.6328125" customWidth="1"/>
+    <col min="1" max="1" width="33.44140625" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.90625" customWidth="1"/>
-    <col min="8" max="8" width="14.90625" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="18.36328125" customWidth="1"/>
+    <col min="13" max="13" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="96"/>
       <c r="B1" s="147" t="s">
         <v>91</v>
@@ -1788,7 +1775,7 @@
       <c r="E1" s="147"/>
       <c r="F1" s="148"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
       <c r="B2" s="113" t="s">
         <v>0</v>
@@ -1798,7 +1785,7 @@
       <c r="E2" s="113"/>
       <c r="F2" s="114"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="113" t="s">
         <v>61</v>
@@ -1808,7 +1795,7 @@
       <c r="E3" s="113"/>
       <c r="F3" s="114"/>
     </row>
-    <row r="4" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="113" t="s">
         <v>62</v>
@@ -1818,7 +1805,7 @@
       <c r="E4" s="113"/>
       <c r="F4" s="114"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>1</v>
       </c>
@@ -1832,7 +1819,7 @@
       <c r="E5" s="113"/>
       <c r="F5" s="114"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>72</v>
       </c>
@@ -1842,7 +1829,7 @@
       <c r="E6" s="113"/>
       <c r="F6" s="114"/>
     </row>
-    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="117" t="s">
         <v>71</v>
       </c>
@@ -1852,43 +1839,43 @@
       <c r="E7" s="115"/>
       <c r="F7" s="116"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="83"/>
       <c r="B8" s="83"/>
       <c r="C8" s="83"/>
       <c r="D8" s="83"/>
     </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="83"/>
       <c r="B9" s="83"/>
       <c r="C9" s="83"/>
       <c r="D9" s="83"/>
     </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="83"/>
       <c r="B10" s="83"/>
       <c r="C10" s="83"/>
       <c r="D10" s="83"/>
     </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="83"/>
       <c r="B11" s="83"/>
       <c r="C11" s="83"/>
       <c r="D11" s="83"/>
     </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="83"/>
       <c r="B12" s="83"/>
       <c r="C12" s="83"/>
       <c r="D12" s="83"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="83"/>
       <c r="B13" s="83"/>
       <c r="C13" s="83"/>
       <c r="D13" s="83"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="83"/>
       <c r="B14" s="151" t="s">
         <v>140</v>
@@ -1896,43 +1883,43 @@
       <c r="C14" s="152"/>
       <c r="D14" s="153"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="83"/>
       <c r="B15" s="154"/>
       <c r="C15" s="155"/>
       <c r="D15" s="156"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="83"/>
       <c r="B16" s="154"/>
       <c r="C16" s="155"/>
       <c r="D16" s="156"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="83"/>
       <c r="B17" s="157"/>
       <c r="C17" s="158"/>
       <c r="D17" s="159"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="83"/>
       <c r="B18" s="83"/>
       <c r="C18" s="83"/>
       <c r="D18" s="83"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="119"/>
       <c r="B19" s="83"/>
       <c r="C19" s="83"/>
       <c r="D19" s="83"/>
     </row>
-    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="83"/>
       <c r="B20" s="83"/>
       <c r="C20" s="83"/>
       <c r="D20" s="83"/>
     </row>
-    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="120" t="s">
         <v>59</v>
       </c>
@@ -1946,7 +1933,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="124" t="s">
         <v>111</v>
       </c>
@@ -1958,7 +1945,7 @@
       <c r="E22" s="88"/>
       <c r="F22" s="88"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="124" t="s">
         <v>98</v>
       </c>
@@ -1976,7 +1963,7 @@
         <v>126855.868739</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="124" t="s">
         <v>2</v>
       </c>
@@ -1995,7 +1982,7 @@
       </c>
       <c r="G24" s="36"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="124" t="s">
         <v>85</v>
       </c>
@@ -2013,7 +2000,7 @@
         <v>6.7956000000000003E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="124"/>
       <c r="B26" s="84"/>
       <c r="C26" s="84"/>
@@ -2027,7 +2014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="125" t="s">
         <v>3</v>
       </c>
@@ -2054,7 +2041,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="126" t="s">
         <v>82</v>
       </c>
@@ -2073,7 +2060,7 @@
       </c>
       <c r="H28" s="66"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="126"/>
       <c r="B29" s="84"/>
       <c r="C29" s="84"/>
@@ -2090,7 +2077,7 @@
       </c>
       <c r="H29" s="66"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="126"/>
       <c r="B30" s="84"/>
       <c r="C30" s="84"/>
@@ -2099,7 +2086,7 @@
       <c r="F30" s="4"/>
       <c r="H30" s="66"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="126"/>
       <c r="B31" s="84"/>
       <c r="C31" s="84"/>
@@ -2108,7 +2095,7 @@
       <c r="F31" s="4"/>
       <c r="H31" s="66"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="125" t="s">
         <v>90</v>
       </c>
@@ -2135,7 +2122,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="126" t="s">
         <v>82</v>
       </c>
@@ -2152,7 +2139,7 @@
       </c>
       <c r="H33" s="66"/>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="84" t="s">
         <v>102</v>
       </c>
@@ -2169,7 +2156,7 @@
       </c>
       <c r="H34" s="66"/>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="126" t="s">
         <v>2</v>
       </c>
@@ -2186,7 +2173,7 @@
       </c>
       <c r="H35" s="66"/>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="125" t="s">
         <v>83</v>
       </c>
@@ -2206,7 +2193,7 @@
       </c>
       <c r="H36" s="66"/>
     </row>
-    <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="127"/>
       <c r="B37" s="107"/>
       <c r="C37" s="107"/>
@@ -2215,7 +2202,7 @@
       <c r="F37" s="46"/>
       <c r="H37" s="66"/>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="127"/>
       <c r="B38" s="107"/>
       <c r="C38" s="107"/>
@@ -2224,7 +2211,7 @@
       <c r="F38" s="46"/>
       <c r="H38" s="66"/>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="107"/>
       <c r="B39" s="107"/>
       <c r="C39" s="128"/>
@@ -2233,7 +2220,7 @@
       <c r="F39" s="46"/>
       <c r="H39" s="66"/>
     </row>
-    <row r="40" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="125" t="s">
         <v>90</v>
       </c>
@@ -2250,7 +2237,7 @@
       </c>
       <c r="H40" s="66"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="126" t="s">
         <v>128</v>
       </c>
@@ -2269,7 +2256,7 @@
       </c>
       <c r="H41" s="66"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="126" t="s">
         <v>135</v>
       </c>
@@ -2288,7 +2275,7 @@
       </c>
       <c r="H42" s="66"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="126" t="s">
         <v>130</v>
       </c>
@@ -2307,7 +2294,7 @@
       </c>
       <c r="H43" s="66"/>
     </row>
-    <row r="44" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="126" t="s">
         <v>134</v>
       </c>
@@ -2326,7 +2313,7 @@
       </c>
       <c r="H44" s="66"/>
     </row>
-    <row r="45" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="125" t="s">
         <v>99</v>
       </c>
@@ -2350,7 +2337,7 @@
       </c>
       <c r="H45" s="66"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="126" t="s">
         <v>4</v>
       </c>
@@ -2361,7 +2348,7 @@
       <c r="F46" s="28"/>
       <c r="H46" s="66"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="126" t="s">
         <v>115</v>
       </c>
@@ -2380,7 +2367,7 @@
       </c>
       <c r="H47" s="66"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="126" t="s">
         <v>5</v>
       </c>
@@ -2402,7 +2389,7 @@
       </c>
       <c r="H48" s="66"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="126" t="s">
         <v>106</v>
       </c>
@@ -2423,7 +2410,7 @@
       </c>
       <c r="H49" s="66"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="125" t="s">
         <v>6</v>
       </c>
@@ -2450,7 +2437,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="84" t="s">
         <v>7</v>
       </c>
@@ -2461,7 +2448,7 @@
       <c r="F51" s="4"/>
       <c r="H51" s="66"/>
     </row>
-    <row r="52" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="130" t="s">
         <v>108</v>
       </c>
@@ -2489,7 +2476,7 @@
       </c>
       <c r="J52" s="81"/>
     </row>
-    <row r="53" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="124" t="s">
         <v>8</v>
       </c>
@@ -2499,11 +2486,11 @@
         <v>0</v>
       </c>
       <c r="E53" s="65">
-        <f t="shared" ref="E53:E59" si="7">D53*91.91%</f>
+        <f t="shared" ref="E53:E57" si="7">D53*91.91%</f>
         <v>0</v>
       </c>
       <c r="F53" s="54">
-        <f t="shared" ref="F53:F59" si="8">D53*8.09%</f>
+        <f t="shared" ref="F53:F57" si="8">D53*8.09%</f>
         <v>0</v>
       </c>
       <c r="G53" s="36">
@@ -2517,7 +2504,7 @@
       <c r="I53" s="81"/>
       <c r="J53" s="81"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="126" t="s">
         <v>113</v>
       </c>
@@ -2545,7 +2532,7 @@
       <c r="I54" s="81"/>
       <c r="J54" s="81"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="126" t="s">
         <v>9</v>
       </c>
@@ -2581,7 +2568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="126" t="s">
         <v>11</v>
       </c>
@@ -2617,7 +2604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="127" t="s">
         <v>10</v>
       </c>
@@ -2653,7 +2640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="134" t="s">
         <v>117</v>
       </c>
@@ -2686,7 +2673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="135" t="s">
         <v>124</v>
       </c>
@@ -2717,7 +2704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="174" t="s">
         <v>125</v>
       </c>
@@ -2742,7 +2729,7 @@
       <c r="I60" s="81"/>
       <c r="J60" s="81"/>
     </row>
-    <row r="61" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="84" t="s">
         <v>92</v>
       </c>
@@ -2773,7 +2760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="171"/>
       <c r="B62" s="172"/>
       <c r="C62" s="173"/>
@@ -2791,7 +2778,7 @@
       <c r="I62" s="81"/>
       <c r="J62" s="81"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="125" t="s">
         <v>12</v>
       </c>
@@ -2822,7 +2809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="84"/>
       <c r="B64" s="84"/>
       <c r="C64" s="84"/>
@@ -2831,7 +2818,7 @@
       <c r="F64" s="4"/>
       <c r="H64" s="66"/>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="84"/>
       <c r="B65" s="84"/>
       <c r="C65" s="84"/>
@@ -2840,7 +2827,7 @@
       <c r="F65" s="4"/>
       <c r="H65" s="66"/>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="84"/>
       <c r="B66" s="84"/>
       <c r="C66" s="84"/>
@@ -2849,7 +2836,7 @@
       <c r="F66" s="4"/>
       <c r="H66" s="66"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="127" t="s">
         <v>110</v>
       </c>
@@ -2869,7 +2856,7 @@
       <c r="G67" s="71"/>
       <c r="H67" s="66"/>
     </row>
-    <row r="68" spans="1:10" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:10" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="174" t="s">
         <v>132</v>
       </c>
@@ -2886,7 +2873,7 @@
       <c r="H68" s="66"/>
       <c r="I68" s="36"/>
     </row>
-    <row r="69" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="125" t="s">
         <v>16</v>
       </c>
@@ -2914,7 +2901,7 @@
       </c>
       <c r="J69" s="36"/>
     </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="84"/>
       <c r="B70" s="84"/>
       <c r="C70" s="84"/>
@@ -2923,7 +2910,7 @@
       <c r="F70" s="4"/>
       <c r="H70" s="66"/>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="84"/>
       <c r="B71" s="84"/>
       <c r="C71" s="84"/>
@@ -2932,7 +2919,7 @@
       <c r="F71" s="4"/>
       <c r="H71" s="66"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="126" t="s">
         <v>13</v>
       </c>
@@ -2943,7 +2930,7 @@
       <c r="F72" s="4"/>
       <c r="H72" s="66"/>
     </row>
-    <row r="73" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="126" t="s">
         <v>14</v>
       </c>
@@ -2967,7 +2954,7 @@
       </c>
       <c r="H73" s="66"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="126" t="s">
         <v>80</v>
       </c>
@@ -2987,7 +2974,7 @@
       <c r="H74" s="66"/>
       <c r="J74" s="39"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="84"/>
       <c r="B75" s="84"/>
       <c r="C75" s="84"/>
@@ -2997,7 +2984,7 @@
       <c r="H75" s="66"/>
       <c r="J75" s="36"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="125"/>
       <c r="B76" s="125"/>
       <c r="C76" s="125"/>
@@ -3023,7 +3010,7 @@
       </c>
       <c r="J76" s="36"/>
     </row>
-    <row r="77" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="126" t="s">
         <v>73</v>
       </c>
@@ -3034,7 +3021,7 @@
       <c r="F77" s="4"/>
       <c r="H77" s="66"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="126" t="s">
         <v>74</v>
       </c>
@@ -3053,7 +3040,7 @@
       </c>
       <c r="H78" s="66"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="126" t="s">
         <v>75</v>
       </c>
@@ -3072,7 +3059,7 @@
       </c>
       <c r="H79" s="66"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="125" t="s">
         <v>15</v>
       </c>
@@ -3099,7 +3086,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="84"/>
       <c r="B81" s="84"/>
       <c r="C81" s="84"/>
@@ -3108,7 +3095,7 @@
       <c r="F81" s="4"/>
       <c r="H81" s="66"/>
     </row>
-    <row r="82" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="139" t="s">
         <v>105</v>
       </c>
@@ -3135,7 +3122,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="140"/>
       <c r="B83" s="83"/>
       <c r="C83" s="83"/>
@@ -3145,7 +3132,7 @@
       <c r="G83" s="68"/>
       <c r="H83" s="66"/>
     </row>
-    <row r="84" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="141" t="s">
         <v>76</v>
       </c>
@@ -3176,14 +3163,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="83"/>
       <c r="B85" s="83"/>
       <c r="C85" s="83"/>
       <c r="D85" s="83"/>
       <c r="E85" s="36"/>
     </row>
-    <row r="86" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="144" t="s">
         <v>112</v>
       </c>
@@ -3192,17 +3179,17 @@
       <c r="D86" s="83"/>
       <c r="E86" s="36"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="C87" s="59"/>
       <c r="E87" s="36"/>
     </row>
-    <row r="88" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="1"/>
       <c r="C88" s="59"/>
       <c r="E88" s="36"/>
     </row>
-    <row r="89" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="61" t="s">
         <v>25</v>
       </c>
@@ -3213,13 +3200,13 @@
       </c>
       <c r="E89" s="36"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E90" s="36"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E91" s="57"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="166" t="s">
         <v>86</v>
       </c>
@@ -3233,7 +3220,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="163"/>
       <c r="B93" s="164"/>
       <c r="C93" s="165"/>
@@ -3247,7 +3234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="168"/>
       <c r="B94" s="169"/>
       <c r="C94" s="170"/>
@@ -3261,7 +3248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" s="160" t="s">
         <v>25</v>
       </c>
@@ -3288,10 +3275,10 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E97" s="36"/>
     </row>
-    <row r="98" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="30" t="s">
         <v>77</v>
       </c>
@@ -3300,7 +3287,7 @@
         <v>8500000</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="32" t="s">
         <v>79</v>
       </c>
@@ -3309,11 +3296,11 @@
         <v>5559993.9100000001</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D100" s="150"/>
       <c r="E100" s="150"/>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="11" t="s">
         <v>63</v>
       </c>
@@ -3322,7 +3309,7 @@
       <c r="D101" s="150"/>
       <c r="E101" s="150"/>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="14" t="s">
         <v>64</v>
       </c>
@@ -3333,7 +3320,7 @@
       <c r="D102" s="150"/>
       <c r="E102" s="150"/>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="16" t="s">
         <v>65</v>
       </c>
@@ -3347,7 +3334,7 @@
       <c r="D103" s="150"/>
       <c r="E103" s="150"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="16" t="s">
         <v>88</v>
       </c>
@@ -3360,7 +3347,7 @@
       <c r="E104" s="150"/>
       <c r="G104" s="39"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="16" t="s">
         <v>87</v>
       </c>
@@ -3373,7 +3360,7 @@
       <c r="E105" s="150"/>
       <c r="G105" s="47"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="16" t="s">
         <v>78</v>
       </c>
@@ -3383,7 +3370,7 @@
       </c>
       <c r="C106" s="17"/>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="16" t="s">
         <v>93</v>
       </c>
@@ -3393,7 +3380,7 @@
       </c>
       <c r="C107" s="17"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="14" t="s">
         <v>67</v>
       </c>
@@ -3403,17 +3390,17 @@
       </c>
       <c r="C108" s="67"/>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="17"/>
       <c r="C109" s="13"/>
       <c r="D109" s="20"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C110" s="13"/>
       <c r="D110" s="36"/>
       <c r="E110" s="81"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="11" t="s">
         <v>68</v>
       </c>
@@ -3425,7 +3412,7 @@
       <c r="E111" s="81"/>
       <c r="F111" s="81"/>
     </row>
-    <row r="112" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="14" t="s">
         <v>122</v>
       </c>
@@ -3436,20 +3423,20 @@
       <c r="D112" s="81"/>
       <c r="E112" s="87"/>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A113" s="14"/>
       <c r="B113" s="80"/>
       <c r="C113" s="19"/>
       <c r="E113" s="36"/>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A114" s="14"/>
       <c r="B114" s="80"/>
       <c r="C114" s="19"/>
       <c r="D114" s="146"/>
       <c r="E114" s="36"/>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A115" s="28" t="s">
         <v>25</v>
       </c>
@@ -3459,42 +3446,42 @@
       </c>
       <c r="C115" s="19"/>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C116" s="20"/>
       <c r="D116" s="81"/>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B117" s="17"/>
       <c r="C117" s="13"/>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N119" s="8"/>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B122" s="149"/>
       <c r="C122" s="149"/>
       <c r="D122" s="149"/>
       <c r="E122" s="149"/>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B123" s="149"/>
       <c r="C123" s="149"/>
       <c r="D123" s="149"/>
       <c r="E123" s="149"/>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B124" s="149"/>
       <c r="C124" s="149"/>
       <c r="D124" s="149"/>
       <c r="E124" s="149"/>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B125" s="149"/>
       <c r="C125" s="149"/>
       <c r="D125" s="149"/>
       <c r="E125" s="149"/>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B126" s="149"/>
       <c r="C126" s="149"/>
       <c r="D126" s="149"/>
@@ -3523,65 +3510,65 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R63"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.54296875" customWidth="1"/>
-    <col min="2" max="2" width="5.90625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="5.36328125" customWidth="1"/>
-    <col min="4" max="4" width="21.6328125" customWidth="1"/>
-    <col min="5" max="5" width="6.08984375" customWidth="1"/>
-    <col min="6" max="7" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.08984375" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="6.109375" customWidth="1"/>
+    <col min="6" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.109375" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="13.6328125" customWidth="1"/>
-    <col min="11" max="11" width="13.36328125" customWidth="1"/>
-    <col min="12" max="12" width="11.54296875" customWidth="1"/>
-    <col min="13" max="13" width="14.36328125" customWidth="1"/>
-    <col min="14" max="14" width="13.6328125" customWidth="1"/>
-    <col min="15" max="15" width="11.453125" customWidth="1"/>
-    <col min="16" max="16" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" customWidth="1"/>
+    <col min="14" max="14" width="13.6640625" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" customWidth="1"/>
+    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="188" t="str">
+    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="189" t="str">
         <f>RESUMEN!C5</f>
         <v>VTO: 13/03</v>
       </c>
-      <c r="B1" s="189"/>
-      <c r="C1" s="189"/>
-      <c r="D1" s="189"/>
-      <c r="E1" s="189"/>
-      <c r="F1" s="189"/>
-      <c r="G1" s="189"/>
-      <c r="H1" s="189"/>
-      <c r="I1" s="189"/>
-      <c r="J1" s="190"/>
+      <c r="B1" s="190"/>
+      <c r="C1" s="190"/>
+      <c r="D1" s="190"/>
+      <c r="E1" s="190"/>
+      <c r="F1" s="190"/>
+      <c r="G1" s="190"/>
+      <c r="H1" s="190"/>
+      <c r="I1" s="190"/>
+      <c r="J1" s="191"/>
       <c r="K1" s="96" t="s">
         <v>96</v>
       </c>
-      <c r="L1" s="177">
+      <c r="L1" s="178">
         <f>RESUMEN!D84</f>
         <v>8500000</v>
       </c>
-      <c r="M1" s="178"/>
+      <c r="M1" s="179"/>
       <c r="N1" s="97"/>
       <c r="O1" s="55">
         <f>L1*8.09%</f>
         <v>687650</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="191"/>
-      <c r="B2" s="192"/>
-      <c r="C2" s="192"/>
-      <c r="D2" s="192"/>
-      <c r="E2" s="192"/>
-      <c r="F2" s="192"/>
-      <c r="G2" s="192"/>
-      <c r="H2" s="192"/>
-      <c r="I2" s="192"/>
-      <c r="J2" s="193"/>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" s="192"/>
+      <c r="B2" s="193"/>
+      <c r="C2" s="193"/>
+      <c r="D2" s="193"/>
+      <c r="E2" s="193"/>
+      <c r="F2" s="193"/>
+      <c r="G2" s="193"/>
+      <c r="H2" s="193"/>
+      <c r="I2" s="193"/>
+      <c r="J2" s="194"/>
       <c r="K2" s="98" t="s">
         <v>97</v>
       </c>
@@ -3595,17 +3582,17 @@
         <v>72051.111500000115</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A3" s="191"/>
-      <c r="B3" s="192"/>
-      <c r="C3" s="192"/>
-      <c r="D3" s="192"/>
-      <c r="E3" s="192"/>
-      <c r="F3" s="192"/>
-      <c r="G3" s="192"/>
-      <c r="H3" s="192"/>
-      <c r="I3" s="192"/>
-      <c r="J3" s="193"/>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" s="192"/>
+      <c r="B3" s="193"/>
+      <c r="C3" s="193"/>
+      <c r="D3" s="193"/>
+      <c r="E3" s="193"/>
+      <c r="F3" s="193"/>
+      <c r="G3" s="193"/>
+      <c r="H3" s="193"/>
+      <c r="I3" s="193"/>
+      <c r="J3" s="194"/>
       <c r="K3" s="98" t="s">
         <v>103</v>
       </c>
@@ -3617,17 +3604,17 @@
       <c r="N3" s="102"/>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" spans="1:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="194"/>
-      <c r="B4" s="195"/>
-      <c r="C4" s="195"/>
-      <c r="D4" s="195"/>
-      <c r="E4" s="195"/>
-      <c r="F4" s="195"/>
-      <c r="G4" s="195"/>
-      <c r="H4" s="195"/>
-      <c r="I4" s="195"/>
-      <c r="J4" s="196"/>
+    <row r="4" spans="1:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="195"/>
+      <c r="B4" s="196"/>
+      <c r="C4" s="196"/>
+      <c r="D4" s="196"/>
+      <c r="E4" s="196"/>
+      <c r="F4" s="196"/>
+      <c r="G4" s="196"/>
+      <c r="H4" s="196"/>
+      <c r="I4" s="196"/>
+      <c r="J4" s="197"/>
       <c r="K4" s="103" t="s">
         <v>97</v>
       </c>
@@ -3641,67 +3628,67 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="181" t="s">
+    <row r="5" spans="1:16" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="182" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="197" t="s">
+      <c r="B5" s="198" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="181" t="s">
+      <c r="C5" s="182" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="186" t="s">
+      <c r="D5" s="187" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="181" t="s">
+      <c r="E5" s="182" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="181" t="s">
+      <c r="F5" s="182" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="181" t="s">
+      <c r="G5" s="182" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="183" t="s">
+      <c r="H5" s="184" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="186" t="s">
+      <c r="I5" s="187" t="s">
         <v>81</v>
       </c>
-      <c r="J5" s="179" t="s">
+      <c r="J5" s="180" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="179" t="s">
+      <c r="K5" s="180" t="s">
         <v>58</v>
       </c>
-      <c r="L5" s="179" t="s">
+      <c r="L5" s="180" t="s">
         <v>136</v>
       </c>
-      <c r="M5" s="179" t="s">
+      <c r="M5" s="180" t="s">
         <v>138</v>
       </c>
-      <c r="N5" s="179" t="s">
+      <c r="N5" s="180" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A6" s="182"/>
-      <c r="B6" s="198"/>
-      <c r="C6" s="182"/>
-      <c r="D6" s="199"/>
-      <c r="E6" s="182"/>
-      <c r="F6" s="182"/>
-      <c r="G6" s="182"/>
-      <c r="H6" s="184"/>
-      <c r="I6" s="187"/>
-      <c r="J6" s="185"/>
-      <c r="K6" s="180"/>
-      <c r="L6" s="185"/>
-      <c r="M6" s="180"/>
-      <c r="N6" s="180"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" s="183"/>
+      <c r="B6" s="199"/>
+      <c r="C6" s="183"/>
+      <c r="D6" s="200"/>
+      <c r="E6" s="183"/>
+      <c r="F6" s="183"/>
+      <c r="G6" s="183"/>
+      <c r="H6" s="185"/>
+      <c r="I6" s="188"/>
+      <c r="J6" s="186"/>
+      <c r="K6" s="181"/>
+      <c r="L6" s="186"/>
+      <c r="M6" s="181"/>
+      <c r="N6" s="181"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>26</v>
       </c>
@@ -3745,7 +3732,7 @@
         <v>651796.00180999993</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>28</v>
       </c>
@@ -3790,7 +3777,7 @@
         <v>220451.31304105348</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>28</v>
       </c>
@@ -3836,7 +3823,7 @@
         <v>422459.39903965255</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>31</v>
       </c>
@@ -3882,7 +3869,7 @@
         <v>284984.53333333333</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>31</v>
       </c>
@@ -3929,7 +3916,7 @@
       </c>
       <c r="P11" s="36"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>34</v>
       </c>
@@ -3975,7 +3962,7 @@
         <v>284984.53333333333</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>34</v>
       </c>
@@ -4021,7 +4008,7 @@
         <v>344189.93313106295</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>36</v>
       </c>
@@ -4064,7 +4051,7 @@
         <v>569969.06666666665</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>36</v>
       </c>
@@ -4105,7 +4092,7 @@
         <v>1032567.0632563261</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>38</v>
       </c>
@@ -4151,7 +4138,7 @@
         <v>284984.61794995336</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>38</v>
       </c>
@@ -4199,7 +4186,7 @@
         <v>365388.68578511506</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>40</v>
       </c>
@@ -4248,7 +4235,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>40</v>
       </c>
@@ -4294,7 +4281,7 @@
         <v>344189.22882741154</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>43</v>
       </c>
@@ -4340,7 +4327,7 @@
         <v>284984.16854183254</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>43</v>
       </c>
@@ -4386,7 +4373,7 @@
         <v>344188.59529363707</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>46</v>
       </c>
@@ -4432,7 +4419,7 @@
         <v>284984.53333333333</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>46</v>
       </c>
@@ -4478,7 +4465,7 @@
         <v>679264.25464429427</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>48</v>
       </c>
@@ -4524,7 +4511,7 @@
         <v>284078.62915967248</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>48</v>
       </c>
@@ -4560,20 +4547,23 @@
         <f t="shared" si="3"/>
         <v>291550</v>
       </c>
-      <c r="L25" s="95"/>
+      <c r="L25" s="95">
+        <f>K25*0.5</f>
+        <v>145775</v>
+      </c>
       <c r="M25" s="3">
         <f t="shared" si="4"/>
-        <v>324706.66666666669</v>
+        <v>470481.66666666669</v>
       </c>
       <c r="N25" s="7">
         <f t="shared" si="1"/>
-        <v>344189.06666666671</v>
+        <v>498710.56666666671</v>
       </c>
       <c r="P25" s="58"/>
       <c r="Q25" s="58"/>
       <c r="R25" s="58"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>50</v>
       </c>
@@ -4617,7 +4607,7 @@
         <v>-370291.22110733407</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>52</v>
       </c>
@@ -4664,7 +4654,7 @@
       </c>
       <c r="R27" s="58"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>54</v>
       </c>
@@ -4710,7 +4700,7 @@
         <v>589990.17829613318</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>56</v>
       </c>
@@ -4751,7 +4741,7 @@
         <v>1773126.346194102</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="48" t="s">
         <v>69</v>
       </c>
@@ -4795,7 +4785,7 @@
         <v>54187.199999999997</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="48" t="s">
         <v>69</v>
       </c>
@@ -4839,7 +4829,7 @@
         <v>55190.666666666664</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="48" t="s">
         <v>69</v>
       </c>
@@ -4883,7 +4873,7 @@
         <v>45156</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="48" t="s">
         <v>69</v>
       </c>
@@ -4927,7 +4917,7 @@
         <v>61211.466666666667</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="48" t="s">
         <v>69</v>
       </c>
@@ -4971,7 +4961,7 @@
         <v>54187.199999999997</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="48" t="s">
         <v>69</v>
       </c>
@@ -5012,7 +5002,7 @@
         <v>150520</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="48" t="s">
         <v>69</v>
       </c>
@@ -5056,7 +5046,7 @@
         <v>50173.333333333336</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="48" t="s">
         <v>69</v>
       </c>
@@ -5100,7 +5090,7 @@
         <v>49169.866666666661</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="48" t="s">
         <v>69</v>
       </c>
@@ -5144,7 +5134,7 @@
         <v>49169.866666666661</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="48" t="s">
         <v>69</v>
       </c>
@@ -5188,7 +5178,7 @@
         <v>59204.533333333333</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="48" t="s">
         <v>69</v>
       </c>
@@ -5232,7 +5222,7 @@
         <v>57197.599999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="48" t="s">
         <v>69</v>
       </c>
@@ -5276,7 +5266,7 @@
         <v>54187.199999999997</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="48" t="s">
         <v>69</v>
       </c>
@@ -5317,7 +5307,7 @@
         <v>165572</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="48" t="s">
         <v>69</v>
       </c>
@@ -5362,7 +5352,7 @@
         <v>72748.111500000581</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="48" t="s">
         <v>69</v>
       </c>
@@ -5403,7 +5393,7 @@
         <v>183634.4</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="48" t="s">
         <v>69</v>
       </c>
@@ -5447,7 +5437,7 @@
         <v>54187.199999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="48" t="s">
         <v>69</v>
       </c>
@@ -5494,7 +5484,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="48" t="s">
         <v>69</v>
       </c>
@@ -5543,7 +5533,7 @@
         <v>-888463.33333333314</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="48" t="s">
         <v>69</v>
       </c>
@@ -5587,7 +5577,7 @@
         <v>49169.866666666661</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="48" t="s">
         <v>69</v>
       </c>
@@ -5632,7 +5622,7 @@
         <v>49169.866666666661</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" s="48" t="s">
         <v>69</v>
       </c>
@@ -5676,7 +5666,7 @@
         <v>59204.533333333333</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" s="48" t="s">
         <v>69</v>
       </c>
@@ -5720,7 +5710,7 @@
         <v>57197.599999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="22"/>
       <c r="B52" s="22"/>
       <c r="C52" s="22"/>
@@ -5749,53 +5739,53 @@
       </c>
       <c r="L52" s="93">
         <f>SUM(L7:L51)</f>
-        <v>20000</v>
+        <v>165775</v>
       </c>
       <c r="M52" s="24">
         <f>SUM(M7:M51)</f>
-        <v>11144970.655459</v>
+        <v>11290745.655459</v>
       </c>
       <c r="N52" s="23">
         <f>SUM(N7:N51)</f>
-        <v>11813668.894786539</v>
+        <v>11968190.394786539</v>
       </c>
       <c r="P52" s="55"/>
     </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="K53" s="58">
         <f>K52-L1</f>
         <v>-72748.111500000581</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C54" s="200"/>
-      <c r="D54" s="200"/>
-      <c r="E54" s="200"/>
-      <c r="F54" s="200"/>
-      <c r="G54" s="200"/>
-      <c r="H54" s="200"/>
-      <c r="I54" s="200"/>
-      <c r="J54" s="200"/>
-      <c r="K54" s="200"/>
-      <c r="L54" s="200"/>
-      <c r="M54" s="200"/>
-      <c r="N54" s="200"/>
-    </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="C55" s="200"/>
-      <c r="D55" s="200"/>
-      <c r="E55" s="200"/>
-      <c r="F55" s="200"/>
-      <c r="G55" s="200"/>
-      <c r="H55" s="200"/>
-      <c r="I55" s="200"/>
-      <c r="J55" s="200"/>
-      <c r="K55" s="200"/>
-      <c r="L55" s="200"/>
-      <c r="M55" s="200"/>
-      <c r="N55" s="200"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C54" s="177"/>
+      <c r="D54" s="177"/>
+      <c r="E54" s="177"/>
+      <c r="F54" s="177"/>
+      <c r="G54" s="177"/>
+      <c r="H54" s="177"/>
+      <c r="I54" s="177"/>
+      <c r="J54" s="177"/>
+      <c r="K54" s="177"/>
+      <c r="L54" s="177"/>
+      <c r="M54" s="177"/>
+      <c r="N54" s="177"/>
+    </row>
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C55" s="177"/>
+      <c r="D55" s="177"/>
+      <c r="E55" s="177"/>
+      <c r="F55" s="177"/>
+      <c r="G55" s="177"/>
+      <c r="H55" s="177"/>
+      <c r="I55" s="177"/>
+      <c r="J55" s="177"/>
+      <c r="K55" s="177"/>
+      <c r="L55" s="177"/>
+      <c r="M55" s="177"/>
+      <c r="N55" s="177"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C56" s="75"/>
       <c r="D56" s="75"/>
       <c r="E56" s="75"/>
@@ -5809,108 +5799,110 @@
       <c r="M56" s="75"/>
       <c r="N56" s="75"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="C57" s="200" t="s">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C57" s="177" t="s">
         <v>101</v>
       </c>
-      <c r="D57" s="200"/>
-      <c r="E57" s="200"/>
-      <c r="F57" s="200"/>
-      <c r="G57" s="200"/>
-      <c r="H57" s="200"/>
-      <c r="I57" s="200"/>
-      <c r="J57" s="200"/>
-      <c r="K57" s="200"/>
-      <c r="L57" s="200"/>
-      <c r="M57" s="200"/>
-      <c r="N57" s="200"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="C58" s="200"/>
-      <c r="D58" s="200"/>
-      <c r="E58" s="200"/>
-      <c r="F58" s="200"/>
-      <c r="G58" s="200"/>
-      <c r="H58" s="200"/>
-      <c r="I58" s="200"/>
-      <c r="J58" s="200"/>
-      <c r="K58" s="200"/>
-      <c r="L58" s="200"/>
-      <c r="M58" s="200"/>
-      <c r="N58" s="200"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="C59" s="200"/>
-      <c r="D59" s="200"/>
-      <c r="E59" s="200"/>
-      <c r="F59" s="200"/>
-      <c r="G59" s="200"/>
-      <c r="H59" s="200"/>
-      <c r="I59" s="200"/>
-      <c r="J59" s="200"/>
-      <c r="K59" s="200"/>
-      <c r="L59" s="200"/>
-      <c r="M59" s="200"/>
-      <c r="N59" s="200"/>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="C60" s="200"/>
-      <c r="D60" s="200"/>
-      <c r="E60" s="200"/>
-      <c r="F60" s="200"/>
-      <c r="G60" s="200"/>
-      <c r="H60" s="200"/>
-      <c r="I60" s="200"/>
-      <c r="J60" s="200"/>
-      <c r="K60" s="200"/>
-      <c r="L60" s="200"/>
-      <c r="M60" s="200"/>
-      <c r="N60" s="200"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="C61" s="200"/>
-      <c r="D61" s="200"/>
-      <c r="E61" s="200"/>
-      <c r="F61" s="200"/>
-      <c r="G61" s="200"/>
-      <c r="H61" s="200"/>
-      <c r="I61" s="200"/>
-      <c r="J61" s="200"/>
-      <c r="K61" s="200"/>
-      <c r="L61" s="200"/>
-      <c r="M61" s="200"/>
-      <c r="N61" s="200"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="C62" s="200"/>
-      <c r="D62" s="200"/>
-      <c r="E62" s="200"/>
-      <c r="F62" s="200"/>
-      <c r="G62" s="200"/>
-      <c r="H62" s="200"/>
-      <c r="I62" s="200"/>
-      <c r="J62" s="200"/>
-      <c r="K62" s="200"/>
-      <c r="L62" s="200"/>
-      <c r="M62" s="200"/>
-      <c r="N62" s="200"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="C63" s="200"/>
-      <c r="D63" s="200"/>
-      <c r="E63" s="200"/>
-      <c r="F63" s="200"/>
-      <c r="G63" s="200"/>
-      <c r="H63" s="200"/>
-      <c r="I63" s="200"/>
-      <c r="J63" s="200"/>
-      <c r="K63" s="200"/>
-      <c r="L63" s="200"/>
-      <c r="M63" s="200"/>
-      <c r="N63" s="200"/>
+      <c r="D57" s="177"/>
+      <c r="E57" s="177"/>
+      <c r="F57" s="177"/>
+      <c r="G57" s="177"/>
+      <c r="H57" s="177"/>
+      <c r="I57" s="177"/>
+      <c r="J57" s="177"/>
+      <c r="K57" s="177"/>
+      <c r="L57" s="177"/>
+      <c r="M57" s="177"/>
+      <c r="N57" s="177"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C58" s="177"/>
+      <c r="D58" s="177"/>
+      <c r="E58" s="177"/>
+      <c r="F58" s="177"/>
+      <c r="G58" s="177"/>
+      <c r="H58" s="177"/>
+      <c r="I58" s="177"/>
+      <c r="J58" s="177"/>
+      <c r="K58" s="177"/>
+      <c r="L58" s="177"/>
+      <c r="M58" s="177"/>
+      <c r="N58" s="177"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C59" s="177"/>
+      <c r="D59" s="177"/>
+      <c r="E59" s="177"/>
+      <c r="F59" s="177"/>
+      <c r="G59" s="177"/>
+      <c r="H59" s="177"/>
+      <c r="I59" s="177"/>
+      <c r="J59" s="177"/>
+      <c r="K59" s="177"/>
+      <c r="L59" s="177"/>
+      <c r="M59" s="177"/>
+      <c r="N59" s="177"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C60" s="177"/>
+      <c r="D60" s="177"/>
+      <c r="E60" s="177"/>
+      <c r="F60" s="177"/>
+      <c r="G60" s="177"/>
+      <c r="H60" s="177"/>
+      <c r="I60" s="177"/>
+      <c r="J60" s="177"/>
+      <c r="K60" s="177"/>
+      <c r="L60" s="177"/>
+      <c r="M60" s="177"/>
+      <c r="N60" s="177"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C61" s="177"/>
+      <c r="D61" s="177"/>
+      <c r="E61" s="177"/>
+      <c r="F61" s="177"/>
+      <c r="G61" s="177"/>
+      <c r="H61" s="177"/>
+      <c r="I61" s="177"/>
+      <c r="J61" s="177"/>
+      <c r="K61" s="177"/>
+      <c r="L61" s="177"/>
+      <c r="M61" s="177"/>
+      <c r="N61" s="177"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C62" s="177"/>
+      <c r="D62" s="177"/>
+      <c r="E62" s="177"/>
+      <c r="F62" s="177"/>
+      <c r="G62" s="177"/>
+      <c r="H62" s="177"/>
+      <c r="I62" s="177"/>
+      <c r="J62" s="177"/>
+      <c r="K62" s="177"/>
+      <c r="L62" s="177"/>
+      <c r="M62" s="177"/>
+      <c r="N62" s="177"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C63" s="177"/>
+      <c r="D63" s="177"/>
+      <c r="E63" s="177"/>
+      <c r="F63" s="177"/>
+      <c r="G63" s="177"/>
+      <c r="H63" s="177"/>
+      <c r="I63" s="177"/>
+      <c r="J63" s="177"/>
+      <c r="K63" s="177"/>
+      <c r="L63" s="177"/>
+      <c r="M63" s="177"/>
+      <c r="N63" s="177"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="C57:N63"/>
     <mergeCell ref="C54:N55"/>
     <mergeCell ref="L1:M1"/>
@@ -5927,8 +5919,6 @@
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
